--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>136007931</v>
       </c>
       <c r="B17" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135840233</v>
+        <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79552</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752313</v>
+        <v>752279</v>
       </c>
       <c r="R2" t="n">
-        <v>7519642</v>
+        <v>7519742</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,28 +761,33 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840233</t>
+          <t>https://artportalen.se/Sighting/136868488</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135840235</v>
+        <v>135840233</v>
       </c>
       <c r="B3" t="n">
         <v>79552</v>
@@ -827,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752243</v>
+        <v>752313</v>
       </c>
       <c r="R3" t="n">
-        <v>7519582</v>
+        <v>7519642</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,16 +893,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840235</t>
+          <t>https://artportalen.se/Sighting/135840233</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135840236</v>
+        <v>135840235</v>
       </c>
       <c r="B4" t="n">
-        <v>83340</v>
+        <v>79552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752248</v>
+        <v>752243</v>
       </c>
       <c r="R4" t="n">
-        <v>7519573</v>
+        <v>7519582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,16 +1005,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840236</t>
+          <t>https://artportalen.se/Sighting/135840235</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135843493</v>
+        <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>92294</v>
+        <v>79555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1022,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752265</v>
+        <v>752385</v>
       </c>
       <c r="R5" t="n">
-        <v>7519590</v>
+        <v>7519741</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,69 +1092,74 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre, hänglavsrik tallskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843493</t>
+          <t>https://artportalen.se/Sighting/136868491</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135843492</v>
+        <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>92315</v>
+        <v>79555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3008</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752404</v>
+        <v>752533</v>
       </c>
       <c r="R6" t="n">
-        <v>7519723</v>
+        <v>7519856</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,69 +1199,74 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog vid myrkant</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843492</t>
+          <t>https://artportalen.se/Sighting/136868495</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135840219</v>
+        <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92023</v>
+        <v>92935</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752299</v>
+        <v>752540</v>
       </c>
       <c r="R7" t="n">
-        <v>7519931</v>
+        <v>7519850</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,31 +1306,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog vid myrkant</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840219</t>
+          <t>https://artportalen.se/Sighting/136868493</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135840223</v>
+        <v>135840236</v>
       </c>
       <c r="B8" t="n">
-        <v>92023</v>
+        <v>83340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752372</v>
+        <v>752248</v>
       </c>
       <c r="R8" t="n">
-        <v>7519864</v>
+        <v>7519573</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,16 +1438,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840223</t>
+          <t>https://artportalen.se/Sighting/135840236</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135843487</v>
+        <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>92767</v>
+        <v>83343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,37 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5454</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752195</v>
+        <v>752535</v>
       </c>
       <c r="R9" t="n">
-        <v>7519938</v>
+        <v>7519859</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1509,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,31 +1525,36 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog vid myrkant</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843487</t>
+          <t>https://artportalen.se/Sighting/136868494</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135840232</v>
+        <v>135843493</v>
       </c>
       <c r="B10" t="n">
-        <v>80092</v>
+        <v>92294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,37 +1562,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752339</v>
+        <v>752265</v>
       </c>
       <c r="R10" t="n">
-        <v>7519644</v>
+        <v>7519590</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1646,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840232</t>
+          <t>https://artportalen.se/Sighting/135843493</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135840211</v>
+        <v>135843492</v>
       </c>
       <c r="B11" t="n">
-        <v>80482</v>
+        <v>92315</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,37 +1674,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>3008</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752189</v>
+        <v>752404</v>
       </c>
       <c r="R11" t="n">
-        <v>7519891</v>
+        <v>7519723</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,49 +1758,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840211</t>
+          <t>https://artportalen.se/Sighting/135843492</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135840213</v>
+        <v>135840219</v>
       </c>
       <c r="B12" t="n">
-        <v>80482</v>
+        <v>92023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1810,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752162</v>
+        <v>752299</v>
       </c>
       <c r="R12" t="n">
-        <v>7519893</v>
+        <v>7519931</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,57 +1875,57 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840213</t>
+          <t>https://artportalen.se/Sighting/135840219</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136007930</v>
+        <v>135840223</v>
       </c>
       <c r="B13" t="n">
-        <v>80594</v>
+        <v>92023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>bergmannivaara, T lm</t>
+          <t>Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752264</v>
+        <v>752372</v>
       </c>
       <c r="R13" t="n">
-        <v>7519899</v>
+        <v>7519864</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,22 +1952,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +1987,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007930</t>
+          <t>https://artportalen.se/Sighting/135840223</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135843491</v>
+        <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,37 +2010,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752361</v>
+        <v>752388</v>
       </c>
       <c r="R14" t="n">
-        <v>7519839</v>
+        <v>7519767</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,27 +2064,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,31 +2080,36 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre, hänglavsrik tallskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843491</t>
+          <t>https://artportalen.se/Sighting/136868492</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135843489</v>
+        <v>135843487</v>
       </c>
       <c r="B15" t="n">
-        <v>58169</v>
+        <v>92767</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103022</v>
+        <v>5454</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,13 +2141,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752370</v>
+        <v>752195</v>
       </c>
       <c r="R15" t="n">
-        <v>7519864</v>
+        <v>7519938</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,7 +2176,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2186,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,58 +2212,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843489</t>
+          <t>https://artportalen.se/Sighting/135843487</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135834021</v>
+        <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>58110</v>
+        <v>91467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>5685</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752226</v>
+        <v>752386</v>
       </c>
       <c r="R16" t="n">
-        <v>7519924</v>
+        <v>7519429</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2322,22 +2283,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,69 +2299,74 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Medelåldrig tallskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135834021</t>
+          <t>https://artportalen.se/Sighting/136868483</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136007931</v>
+        <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>98213</v>
+        <v>78879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>bergmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752255</v>
+        <v>752273</v>
       </c>
       <c r="R17" t="n">
-        <v>7519894</v>
+        <v>7519725</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,22 +2390,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,31 +2406,36 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007931</t>
+          <t>https://artportalen.se/Sighting/136868487</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135840222</v>
+        <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>79496</v>
+        <v>83463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,37 +2443,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>260591</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752348</v>
+        <v>752422</v>
       </c>
       <c r="R18" t="n">
-        <v>7519890</v>
+        <v>7519854</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2546,22 +2497,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,31 +2513,36 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog med örtinslag</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840222</t>
+          <t>https://artportalen.se/Sighting/136868499</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135840227</v>
+        <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79496</v>
+        <v>79233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,37 +2550,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>260591</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752367</v>
+        <v>752450</v>
       </c>
       <c r="R19" t="n">
-        <v>7519787</v>
+        <v>7519607</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2658,22 +2604,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,34 +2618,38 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840227</t>
+          <t>https://artportalen.se/Sighting/136868485</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135840228</v>
+        <v>135840232</v>
       </c>
       <c r="B20" t="n">
-        <v>79496</v>
+        <v>80092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>260591</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752378</v>
+        <v>752339</v>
       </c>
       <c r="R20" t="n">
-        <v>7519790</v>
+        <v>7519644</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2776,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,7 +2752,1886 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135840232</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136868481</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>752402</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7519378</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Medelåldrig tallskog på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868481</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136868484</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>752521</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7519568</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandad, äldre sumpskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868484</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136868489</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>752306</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7519714</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868489</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136868497</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>752468</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7519871</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gles, äldre tallskog på bärris</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868497</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135840211</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80482</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>752189</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7519891</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840211</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135840213</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80482</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>752162</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7519893</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840213</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136007930</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80594</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>bergmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>752264</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7519899</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007930</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135843491</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergsmannijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>752361</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7519839</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135843491</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135843489</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergsmannijärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>752370</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7519864</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135843489</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135834021</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58110</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>752226</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7519924</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135834021</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136007931</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>bergmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>752255</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7519894</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007931</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136868490</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>752305</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7519714</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868490</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135840222</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>752348</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7519890</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840222</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135840227</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>752367</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7519787</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840227</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135840228</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>752378</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7519790</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135840228</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136868486</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>752418</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7519642</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Medelåldrig tallskog på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868486</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136868498</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>752447</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7519863</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Gles, äldre tallskog på bärris</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868498</t>
         </is>
       </c>
     </row>
@@ -2837,6 +4656,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92935</v>
+        <v>92937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91467</v>
+        <v>91469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136868490</v>
       </c>
       <c r="B32" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136868486</v>
       </c>
       <c r="B36" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>136868498</v>
       </c>
       <c r="B37" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92937</v>
+        <v>92939</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91469</v>
+        <v>91471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136868490</v>
       </c>
       <c r="B32" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136868486</v>
       </c>
       <c r="B36" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>136868498</v>
       </c>
       <c r="B37" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,10 +3298,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135840213</v>
+        <v>136007930</v>
       </c>
       <c r="B26" t="n">
-        <v>80482</v>
+        <v>80594</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3309,37 +3309,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>bergmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752162</v>
+        <v>752264</v>
       </c>
       <c r="R26" t="n">
-        <v>7519893</v>
+        <v>7519899</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3363,22 +3363,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,60 +3398,60 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840213</t>
+          <t>https://artportalen.se/Sighting/136007930</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136007930</v>
+        <v>135843491</v>
       </c>
       <c r="B27" t="n">
-        <v>80594</v>
+        <v>58006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>bergmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752264</v>
+        <v>752361</v>
       </c>
       <c r="R27" t="n">
-        <v>7519899</v>
+        <v>7519839</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3475,22 +3475,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,27 +3510,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007930</t>
+          <t>https://artportalen.se/Sighting/135843491</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135843491</v>
+        <v>135843489</v>
       </c>
       <c r="B28" t="n">
-        <v>58006</v>
+        <v>58169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,21 +3538,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3557,13 +3562,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752361</v>
+        <v>752370</v>
       </c>
       <c r="R28" t="n">
-        <v>7519839</v>
+        <v>7519864</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3592,7 +3597,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3602,12 +3607,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3633,16 +3633,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843491</t>
+          <t>https://artportalen.se/Sighting/135843489</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135843489</v>
+        <v>135834021</v>
       </c>
       <c r="B29" t="n">
-        <v>58169</v>
+        <v>58110</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,37 +3650,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752370</v>
+        <v>752226</v>
       </c>
       <c r="R29" t="n">
-        <v>7519864</v>
+        <v>7519924</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3709,7 +3713,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3719,7 +3723,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3734,69 +3738,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843489</t>
+          <t>https://artportalen.se/Sighting/135834021</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135834021</v>
+        <v>136007931</v>
       </c>
       <c r="B30" t="n">
-        <v>58110</v>
+        <v>98213</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
+          <t>bergmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752226</v>
+        <v>752255</v>
       </c>
       <c r="R30" t="n">
-        <v>7519924</v>
+        <v>7519894</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3820,22 +3820,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3850,65 +3850,65 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135834021</t>
+          <t>https://artportalen.se/Sighting/136007931</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136007931</v>
+        <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>98213</v>
+        <v>80072</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>bergmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752255</v>
+        <v>752305</v>
       </c>
       <c r="R31" t="n">
-        <v>7519894</v>
+        <v>7519714</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3932,22 +3932,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3958,31 +3948,36 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007931</t>
+          <t>https://artportalen.se/Sighting/136868490</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136868490</v>
+        <v>135840222</v>
       </c>
       <c r="B32" t="n">
-        <v>80072</v>
+        <v>79496</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,37 +3985,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+          <t>Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752305</v>
+        <v>752348</v>
       </c>
       <c r="R32" t="n">
-        <v>7519714</v>
+        <v>7519890</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4044,12 +4039,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,33 +4065,28 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog på blåbärsris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136868490</t>
+          <t>https://artportalen.se/Sighting/135840222</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135840222</v>
+        <v>135840227</v>
       </c>
       <c r="B33" t="n">
         <v>79496</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752348</v>
+        <v>752367</v>
       </c>
       <c r="R33" t="n">
-        <v>7519890</v>
+        <v>7519787</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,6 +4175,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4192,13 +4193,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840222</t>
+          <t>https://artportalen.se/Sighting/135840227</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135840227</v>
+        <v>135840228</v>
       </c>
       <c r="B34" t="n">
         <v>79496</v>
@@ -4233,10 +4234,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752367</v>
+        <v>752378</v>
       </c>
       <c r="R34" t="n">
-        <v>7519787</v>
+        <v>7519790</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4287,7 +4288,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4305,16 +4305,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840227</t>
+          <t>https://artportalen.se/Sighting/135840228</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135840228</v>
+        <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79496</v>
+        <v>79505</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,17 +4342,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752378</v>
+        <v>752418</v>
       </c>
       <c r="R35" t="n">
-        <v>7519790</v>
+        <v>7519642</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4376,22 +4376,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4402,28 +4392,33 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Medelåldrig tallskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840228</t>
+          <t>https://artportalen.se/Sighting/136868486</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136868486</v>
+        <v>136868498</v>
       </c>
       <c r="B36" t="n">
         <v>79505</v>
@@ -4458,10 +4453,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752418</v>
+        <v>752447</v>
       </c>
       <c r="R36" t="n">
-        <v>7519642</v>
+        <v>7519863</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4507,7 +4502,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Medelåldrig tallskog på blåbärsris</t>
+          <t>Gles, äldre tallskog på bärris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4523,113 +4518,6 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136868486</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>136868498</v>
-      </c>
-      <c r="B37" t="n">
-        <v>79505</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>752447</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7519863</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Gles, äldre tallskog på bärris</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136868498</t>
         </is>
@@ -4672,7 +4560,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92939</v>
+        <v>92940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92940</v>
+        <v>92946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92946</v>
+        <v>92950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91478</v>
+        <v>91482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92950</v>
+        <v>92952</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92952</v>
+        <v>92965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91484</v>
+        <v>91497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92965</v>
+        <v>92967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92967</v>
+        <v>92970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92970</v>
+        <v>92980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91502</v>
+        <v>91512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92980</v>
+        <v>92981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92981</v>
+        <v>92984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92984</v>
+        <v>92986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92986</v>
+        <v>92992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>92992</v>
+        <v>93004</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 32844-2026 artfynd.xlsx
+++ b/artfynd/A 32844-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868488</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868491</v>
       </c>
       <c r="B5" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868495</v>
       </c>
       <c r="B6" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136868493</v>
       </c>
       <c r="B7" t="n">
-        <v>93004</v>
+        <v>93005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136868494</v>
       </c>
       <c r="B9" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136868492</v>
       </c>
       <c r="B14" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136868483</v>
       </c>
       <c r="B16" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136868487</v>
       </c>
       <c r="B17" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136868499</v>
       </c>
       <c r="B18" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136868485</v>
       </c>
       <c r="B19" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136868481</v>
       </c>
       <c r="B21" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>136868484</v>
       </c>
       <c r="B22" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136868489</v>
       </c>
       <c r="B23" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>136868497</v>
       </c>
       <c r="B24" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136868490</v>
       </c>
       <c r="B31" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>136868486</v>
       </c>
       <c r="B35" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>136868498</v>
       </c>
       <c r="B36" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
